--- a/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>6.033133846197725</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>5.22416001938999</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>5.544045139431475</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>7.850866450249439</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>6.419846071159641</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         <v>7.062696255129719</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         <v>6.935000525806445</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -606,7 +606,7 @@
         <v>7.000792140377277</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -633,13 +633,13 @@
         <v>6.974429320498854</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>1015652.19</v>
+        <v>945219.25</v>
       </c>
       <c r="D11">
-        <v>956714.3100000001</v>
+        <v>888737.6899999999</v>
       </c>
       <c r="E11">
-        <v>58937.87999999989</v>
+        <v>56481.56000000006</v>
       </c>
       <c r="F11">
-        <v>6.160447208111686</v>
+        <v>6.3552565211902</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -675,45 +675,126 @@
         </is>
       </c>
       <c r="C12">
-        <v>1147772</v>
+        <v>1046954.88</v>
       </c>
       <c r="D12">
-        <v>1094217.38</v>
+        <v>991826.38</v>
       </c>
       <c r="E12">
-        <v>53554.62000000011</v>
+        <v>55128.5</v>
       </c>
       <c r="F12">
-        <v>4.894330960087667</v>
+        <v>5.558281279027888</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>1003583.69</v>
+      </c>
+      <c r="D13">
+        <v>947770.4399999999</v>
+      </c>
+      <c r="E13">
+        <v>55813.25</v>
+      </c>
+      <c r="F13">
+        <v>5.888899636920519</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Talca</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>1015652.19</v>
+      </c>
+      <c r="D14">
+        <v>956714.3100000001</v>
+      </c>
+      <c r="E14">
+        <v>58937.87999999989</v>
+      </c>
+      <c r="F14">
+        <v>6.160447208111686</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>1147772</v>
+      </c>
+      <c r="D15">
+        <v>1094217.38</v>
+      </c>
+      <c r="E15">
+        <v>53554.62000000011</v>
+      </c>
+      <c r="F15">
+        <v>4.894330960087667</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>1091864.62</v>
       </c>
-      <c r="D13">
+      <c r="D16">
         <v>1035701.06</v>
       </c>
-      <c r="E13">
+      <c r="E16">
         <v>56163.56000000006</v>
       </c>
-      <c r="F13">
+      <c r="F16">
         <v>5.422757798471323</v>
       </c>
-      <c r="G13">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -786,7 +867,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1027,6 +1108,60 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>833765.75</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>947770.4399999999</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>1003583.69</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:04</t>
+    <t xml:space="preserve">2026-07-30 18:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -86,13 +86,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_a_2024_maule.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de asalariados formales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Maule</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -905,23 +911,23 @@
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -1001,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -1012,7 +1018,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>766805.19</v>
@@ -1023,7 +1029,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>888919.44</v>
@@ -1034,7 +1040,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>951701.12</v>
@@ -1045,7 +1051,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>790198.38</v>
@@ -1056,7 +1062,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>891678.69</v>
@@ -1067,7 +1073,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>953868.19</v>
@@ -1078,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>778968.44</v>
@@ -1089,7 +1095,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>888876.06</v>
@@ -1100,7 +1106,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>938155.75</v>
@@ -1111,7 +1117,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>910150.81</v>
@@ -1122,7 +1128,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>1035701.06</v>
@@ -1133,7 +1139,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1091864.62</v>
@@ -1144,7 +1150,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>833765.75</v>
@@ -1155,7 +1161,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>947770.44</v>
@@ -1166,7 +1172,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>1003583.69</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 18:05</t>
+    <t xml:space="preserve">2026-08-19 15:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:17</t>
+    <t xml:space="preserve">2026-09-07 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
